--- a/appointment_checklist_forms/036_wedding_planning_appointment_checklist_form_template--appointment_checklist_forms.xlsx
+++ b/appointment_checklist_forms/036_wedding_planning_appointment_checklist_form_template--appointment_checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1153,8 +1153,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'engagement_meeting',_'value':_'engagement_meeting'}</t>
+          <t>engagement_meeting</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Engagement Meeting', 'value': 'Engagement Meeting'}</t>
+          <t>Engagement Meeting</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'venue_visit',_'value':_'venue_visit'}</t>
+          <t>venue_visit</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Venue Visit', 'value': 'Venue Visit'}</t>
+          <t>Venue Visit</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'cake_tasting',_'value':_'cake_tasting'}</t>
+          <t>cake_tasting</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Cake Tasting', 'value': 'Cake Tasting'}</t>
+          <t>Cake Tasting</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'rsvps',_'value':_'rsvps'}</t>
+          <t>rsvps</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'RSVPs', 'value': 'RSVPs'}</t>
+          <t>RSVPs</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'invitations',_'value':_'invitations'}</t>
+          <t>invitations</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Invitations', 'value': 'Invitations'}</t>
+          <t>Invitations</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'seating',_'value':_'seating'}</t>
+          <t>seating</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Seating', 'value': 'Seating'}</t>
+          <t>Seating</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'rehearsal_dinner',_'value':_'rehearsal_dinner'}</t>
+          <t>rehearsal_dinner</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Rehearsal Dinner', 'value': 'Rehearsal Dinner'}</t>
+          <t>Rehearsal Dinner</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'rehearsal_lunch',_'value':_'rehearsal_lunch'}</t>
+          <t>rehearsal_lunch</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Rehearsal Lunch', 'value': 'Rehearsal Lunch'}</t>
+          <t>Rehearsal Lunch</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'full',_'value':_'full'}</t>
+          <t>full</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Full', 'value': 'Full'}</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'partial',_'value':_'partial'}</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Partial', 'value': 'Partial'}</t>
+          <t>Partial</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
